--- a/spec-tech/ig/StructureDefinition-xdmAuthorInstitution.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmAuthorInstitution.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T14:32:10+00:00</t>
+    <t>2026-07-23T16:03:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdmAuthorInstitution.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmAuthorInstitution.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T16:03:49+00:00</t>
+    <t>2026-07-23T16:11:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdmAuthorInstitution.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmAuthorInstitution.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T16:11:23+00:00</t>
+    <t>2026-07-27T13:36:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdmAuthorInstitution.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmAuthorInstitution.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T13:36:25+00:00</t>
+    <t>2026-07-30T09:32:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -338,7 +338,7 @@
     <t>xdmAuthorInstitution.XON10</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/structIdNat
+    <t xml:space="preserve">string {https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/structIdNat|0.1.0}
 </t>
   </si>
   <si>
@@ -660,7 +660,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="58.8046875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="70.34375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/spec-tech/ig/StructureDefinition-xdmAuthorInstitution.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmAuthorInstitution.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T09:32:03+00:00</t>
+    <t>2026-07-30T15:04:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdmAuthorInstitution.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmAuthorInstitution.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T15:04:16+00:00</t>
+    <t>2026-08-07T08:28:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -260,7 +260,7 @@
     <t>AuthorInstitution</t>
   </si>
   <si>
-    <t>xdmAuthorInstitution.XON1</t>
+    <t>xdmAuthorInstitution.xon1</t>
   </si>
   <si>
     <t>1</t>
@@ -282,7 +282,7 @@
     <t>NA</t>
   </si>
   <si>
-    <t>xdmAuthorInstitution.XON6</t>
+    <t>xdmAuthorInstitution.xon6</t>
   </si>
   <si>
     <t xml:space="preserve">Base
@@ -295,13 +295,13 @@
     <t>Identifiant de l’organisme gérant l’identifiant de la structure. Cet identifiant, au format HL7 v.2.5 est constitué de trois sous-composants qui prennent les valeurs suivantes.</t>
   </si>
   <si>
-    <t>xdmAuthorInstitution.XON6.composant1</t>
+    <t>xdmAuthorInstitution.xon6.composant1</t>
   </si>
   <si>
     <t>Vide, pas de valeur</t>
   </si>
   <si>
-    <t>xdmAuthorInstitution.XON6.composant2</t>
+    <t>xdmAuthorInstitution.xon6.composant2</t>
   </si>
   <si>
     <t>Valeur de Universal ID</t>
@@ -313,13 +313,13 @@
     <t>author/assignedAuthor/representedOrganization/id@root (Si l’élément id fait l’objet d’un nullFlavor dans l’en-tête CDA, les composants 6, 7 et 10 de la métadonnée authorInstitution doivent être vides)</t>
   </si>
   <si>
-    <t>xdmAuthorInstitution.XON6.composant3</t>
+    <t>xdmAuthorInstitution.xon6.composant3</t>
   </si>
   <si>
     <t>Valeur de Universal ID type (ID)</t>
   </si>
   <si>
-    <t>xdmAuthorInstitution.XON7</t>
+    <t>xdmAuthorInstitution.xon7</t>
   </si>
   <si>
     <t xml:space="preserve">code
@@ -335,7 +335,7 @@
     <t>Valeur ne provenant pas de l’en-tête CDA</t>
   </si>
   <si>
-    <t>xdmAuthorInstitution.XON10</t>
+    <t>xdmAuthorInstitution.xon10</t>
   </si>
   <si>
     <t xml:space="preserve">string {https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/structIdNat|0.1.0}
@@ -650,8 +650,8 @@
   <dimension ref="A1:AL9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="32.80078125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="32.80078125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="32.19921875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="32.19921875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -681,7 +681,7 @@
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="32.80078125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="32.19921875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
